--- a/data/pokemon-shiny/legendary_mythical_shiny_master.xlsx
+++ b/data/pokemon-shiny/legendary_mythical_shiny_master.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Legend" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Master'!$A$1:$Y$109</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Master'!$A$1:$Y$118</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y109"/>
+  <dimension ref="A1:Y118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Normal, Attack, Defense, Speed — all four shiny in GO raids (separate 2020–2022 dates); main-series forme is set by in-game meteorites/version, all huntable</t>
+          <t>This row is the Normal Forme. Attack / Defense / Speed Formes each have their OWN row (each a separate GO shiny with its own release date)</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -3747,7 +3747,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Origin Forme — shiny available (GO; main-series via Adamant Crystal in PLA, shiny-locked there)</t>
+          <t>Origin Forme — see its own row (separate GO shiny)</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Origin Forme — shiny available in GO (Lustrous Globe in PLA is shiny-locked)</t>
+          <t>Origin Forme — see its own row (separate GO shiny)</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Altered Forme &amp; Origin Forme — both shiny in GO</t>
+          <t>This row is the Altered Forme. Origin Forme — see its own row (separate GO shiny)</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -4914,22 +4914,22 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>D (shiny unavailable)</t>
+          <t>A (true hunt, current)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Brilliant Diamond:1/4096</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
@@ -5014,7 +5014,7 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>No legitimate shiny Arceus as of Aug 2026 (a disputed BDSP claim aside). Classified SHINY UNAVAILABLE.</t>
+          <t>Shiny Arceus IS legitimately huntable — the BDSP Hall of Origin encounter (Azure Flute) is not shiny-locked, so you can soft-reset for it (flat 1/4096; BDSP Shiny Charm does not help). PLA and all distributions are locked.</t>
         </is>
       </c>
     </row>
@@ -5644,7 +5644,7 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Incarnate &amp; Therian — both shiny in GO (Therian released 2022)</t>
+          <t>This row is the Incarnate Forme. Therian Forme — see its own row (separate GO shiny)</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Incarnate &amp; Therian — both shiny in GO (Therian released 2022)</t>
+          <t>This row is the Incarnate Forme. Therian Forme — see its own row (separate GO shiny)</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Incarnate &amp; Therian — both shiny in GO (Therian released 2022)</t>
+          <t>This row is the Incarnate Forme. Therian Forme — see its own row (separate GO shiny)</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
@@ -14289,8 +14289,1151 @@
         </is>
       </c>
     </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Deoxys (Attack Forme)</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Mythical</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Deoxys</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>A (true hunt, current)</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>FireRed (Gen 3):1/8192</t>
+        </is>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>~1/20</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Forme-specific raids (shiny since Feb 19 2022) — RNG; ~1/20</t>
+        </is>
+      </c>
+      <c r="X110" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>Alternate Forme of Deoxys — a separate shiny collectible in GO (own release date). In the main series the Forme is fixed by game/meteorite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Deoxys (Defense Forme)</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Mythical</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Deoxys</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>A (true hunt, current)</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>LeafGreen (Gen 3):1/8192</t>
+        </is>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>~1/20</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Forme-specific raids (shiny since Feb 22 2022) — RNG; ~1/20</t>
+        </is>
+      </c>
+      <c r="X111" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>Alternate Forme of Deoxys — a separate shiny collectible in GO (own release date). In the main series the Forme is fixed by game/meteorite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Deoxys (Speed Forme)</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Mythical</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Deoxys</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>A (true hunt, current)</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>Emerald (Gen 3):1/8192</t>
+        </is>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>~1/20</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Forme-specific raids (shiny since Feb 25 2022) — RNG; ~1/20</t>
+        </is>
+      </c>
+      <c r="X112" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>Alternate Forme of Deoxys — a separate shiny collectible in GO (own release date). In the main series the Forme is fixed by game/meteorite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Giratina (Origin Forme)</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Giratina</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>A (true hunt, current)</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>~1/20</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Origin Forme raids — RNG; ~1/20</t>
+        </is>
+      </c>
+      <c r="X113" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>Separate shiny raid boss in GO; in the main series it's a Griseous Orb/Core form-change of your Giratina.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Dialga (Origin Forme)</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Dialga</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>A (true hunt, current)</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>~1/20</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Origin Forme raids — RNG; ~1/20</t>
+        </is>
+      </c>
+      <c r="X114" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>Separate shiny raid boss in GO; main-series Origin form via the Adamant Crystal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Palkia (Origin Forme)</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Palkia</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>A (true hunt, current)</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R115" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>~1/20</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Origin Forme raids — RNG; ~1/20</t>
+        </is>
+      </c>
+      <c r="X115" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>Separate shiny raid boss in GO; main-series Origin form via the Lustrous Globe.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Tornadus (Therian Forme)</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Tornadus</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>A (true hunt, current)</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>~1/20</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Therian Forme raids (shiny since Mar 15 2022) — RNG; ~1/20</t>
+        </is>
+      </c>
+      <c r="X116" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>Separate shiny raid boss in GO; in the main series it's a Reveal Glass form-change of the Incarnate forme.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Thundurus (Therian Forme)</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Thundurus</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>A (true hunt, current)</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R117" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>~1/20</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Therian Forme raids (shiny since Apr 5 2022) — RNG; ~1/20</t>
+        </is>
+      </c>
+      <c r="X117" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>Separate shiny raid boss in GO; in the main series it's a Reveal Glass form-change of the Incarnate forme.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Landorus (Therian Forme)</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Landorus</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>A (true hunt, current)</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R118" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>~1/20</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Therian Forme raids (shiny since Apr 26 2022) — RNG; ~1/20</t>
+        </is>
+      </c>
+      <c r="X118" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>Separate shiny raid boss in GO; in the main series it's a Reveal Glass form-change of the Incarnate forme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Y109"/>
+  <autoFilter ref="A1:Y118"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/pokemon-shiny/legendary_mythical_shiny_master.xlsx
+++ b/data/pokemon-shiny/legendary_mythical_shiny_master.xlsx
@@ -1121,22 +1121,22 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No (historical only)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>B (guaranteed reward)</t>
+          <t>E (hunt, historical only)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Emerald (Japan, Old Sea Map):1/8192</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Shiny via 'All-in-One #151' Masterwork (guaranteed; $5). Not RNG-huntable.</t>
+          <t>Shiny via 'All-in-One #151' Masterwork (guaranteed; $5). Not RNG-huntable in GO.</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>No legitimate main-series shiny Mew has ever existed. Shiny exists only as a guaranteed GO reward.</t>
+          <t>Correction: shiny Mew IS a (historical) self-catch hunt via the Japan-only Old Sea Map (Faraway Island, Emerald), 1/8192 — long discontinued. Also a guaranteed GO Masterwork shiny.</t>
         </is>
       </c>
     </row>
@@ -6946,22 +6946,22 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>D (shiny unavailable)</t>
+          <t>A (true hunt, current)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -6986,7 +6986,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1/300 (1/100 charm)</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>No legitimate shiny Zygarde exists anywhere as of Aug 2026. SHINY UNAVAILABLE.</t>
+          <t>Correction: shiny Zygarde IS huntable — Sword/Shield Dynamax Adventures (Max Lair) is the only game where you can catch it, 1/300 (1/100 with Shiny Charm). Every story/static/cell-assembly encounter is shiny-locked; no guaranteed shiny Zygarde has ever been officially distributed.</t>
         </is>
       </c>
     </row>
@@ -7554,7 +7554,7 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>Officially 'Synthetic Pokémon'; Bulbapedia counts it as Legendary. Shiny UNAVAILABLE (gift is the only source and is locked).</t>
+          <t>Officially 'Synthetic Pokémon'; Bulbapedia counts it as Legendary. No legit shiny Type: Null: the gift is shiny-locked everywhere, and the 2017 event distributed the already-evolved Shiny SILVALLY (you cannot devolve it). So shiny Silvally exists, but shiny Type: Null does not.</t>
         </is>
       </c>
     </row>
@@ -7581,7 +7581,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>D (shiny unavailable)</t>
+          <t>C (event distribution only)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -7681,7 +7681,7 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>Gained Legendary status Oct 2017. Shiny UNAVAILABLE (only from shiny-locked Type: Null).</t>
+          <t>Correction: a legit shiny Silvally EXISTS via the official 2017 GameStop/GAME/EB event distribution (already evolved) — but it is NOT RNG-huntable. The in-game Type: Null gift is shiny-locked everywhere.</t>
         </is>
       </c>
     </row>
@@ -9105,7 +9105,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>D (shiny unavailable)</t>
+          <t>C (event distribution only)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -9205,7 +9205,7 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>No legitimate shiny Zeraora as of Aug 2026 (future GO release rumored). SHINY UNAVAILABLE currently.</t>
+          <t>Correction: a legit shiny Zeraora EXISTS via the 2020 Pokémon HOME raid-milestone distribution (guaranteed, event over) — but it is NOT RNG-huntable. Not shiny in GO as of Aug 2026.</t>
         </is>
       </c>
     </row>
@@ -11110,7 +11110,7 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>Shiny exists ONLY via the 2026 guaranteed retail-code distribution. Never RNG-huntable.</t>
+          <t>Shiny exists ONLY via the 2025 guaranteed retail-code distribution (Sep 26–Oct 15 2025). Never RNG-huntable.</t>
         </is>
       </c>
     </row>
@@ -11237,7 +11237,7 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>Shiny exists ONLY via the 2026 guaranteed retail-code distribution. Never RNG-huntable.</t>
+          <t>Shiny exists ONLY via the 2025 guaranteed retail-code distribution (Sep 26–Oct 15 2025). Never RNG-huntable.</t>
         </is>
       </c>
     </row>

--- a/data/pokemon-shiny/legendary_mythical_shiny_master.xlsx
+++ b/data/pokemon-shiny/legendary_mythical_shiny_master.xlsx
@@ -14920,7 +14920,7 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>Separate shiny raid boss in GO; main-series Origin form via the Adamant Crystal.</t>
+          <t>GO-ONLY shiny. Unlike Giratina, a shiny Origin Dialga can only come from Pokémon GO: the Adamant Crystal is PLA-exclusive and the PLA Dialga is shiny-locked, so it can't be paired with a huntable shiny.</t>
         </is>
       </c>
     </row>
@@ -15047,7 +15047,7 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>Separate shiny raid boss in GO; main-series Origin form via the Lustrous Globe.</t>
+          <t>GO-ONLY shiny. Unlike Giratina, a shiny Origin Palkia can only come from Pokémon GO: the Lustrous Globe is PLA-exclusive and the PLA Palkia is shiny-locked, so it can't be paired with a huntable shiny.</t>
         </is>
       </c>
     </row>

--- a/data/pokemon-shiny/legendary_mythical_shiny_master.xlsx
+++ b/data/pokemon-shiny/legendary_mythical_shiny_master.xlsx
@@ -7454,22 +7454,22 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>D (shiny unavailable)</t>
+          <t>A (true hunt, current)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>shiny-locked</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
@@ -7524,7 +7524,7 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Sun:1/4096</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>Officially 'Synthetic Pokémon'; Bulbapedia counts it as Legendary. No legit shiny Type: Null: the gift is shiny-locked everywhere, and the 2017 event distributed the already-evolved Shiny SILVALLY (you cannot devolve it). So shiny Silvally exists, but shiny Type: Null does not.</t>
+          <t>Correction: shiny Type: Null IS huntable — Gladion's gift in Sun/Moon &amp; Ultra Sun/Ultra Moon is not shiny-locked (soft-reset, full odds; gifts ignore the Shiny Charm). Only the SwSh gift is locked.</t>
         </is>
       </c>
     </row>
@@ -7586,22 +7586,22 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>C (event distribution only)</t>
+          <t>A (true hunt, current)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Sun:1/4096</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
@@ -7681,7 +7681,7 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>Correction: a legit shiny Silvally EXISTS via the official 2017 GameStop/GAME/EB event distribution (already evolved) — but it is NOT RNG-huntable. The in-game Type: Null gift is shiny-locked everywhere.</t>
+          <t>Correction: shiny Silvally IS huntable — evolve a soft-reset shiny Type: Null from Sun/Moon or USUM (the Gen 7 gift isn't locked). A guaranteed shiny was also officially distributed in 2017.</t>
         </is>
       </c>
     </row>
@@ -13677,22 +13677,22 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>D (shiny unavailable)</t>
+          <t>A (true hunt, current)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -13732,7 +13732,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>shiny-locked</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
@@ -13747,7 +13747,7 @@
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Ultra Sun:1/4096</t>
         </is>
       </c>
       <c r="T105" t="inlineStr">
@@ -13777,7 +13777,7 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>Ultra Beast. Shiny UNAVAILABLE (shiny-locked in both USUM and GO).</t>
+          <t>Correction: shiny Poipole IS huntable — the Ultra Sun/Ultra Moon Ultra Recon Squad gift is not shiny-locked (soft-reset, full odds). Shiny-locked in SwSh Crown Tundra and in GO.</t>
         </is>
       </c>
     </row>
@@ -13804,22 +13804,22 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>D (shiny unavailable)</t>
+          <t>A (true hunt, current)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Ultra Sun:1/4096</t>
         </is>
       </c>
       <c r="T106" t="inlineStr">
@@ -13884,7 +13884,7 @@
       </c>
       <c r="U106" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="V106" t="inlineStr">
@@ -13904,7 +13904,7 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>Ultra Beast. Shiny UNAVAILABLE (only from shiny-locked Poipole).</t>
+          <t>Correction: shiny Naganadel IS huntable — evolve a soft-reset shiny Poipole from USUM. Shiny-locked in GO.</t>
         </is>
       </c>
     </row>
